--- a/VRPExample/heuristicapproach/src/furgoni2.xlsx
+++ b/VRPExample/heuristicapproach/src/furgoni2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\Documents\EPFL\Full-Optimizer\VRPExample\heuristicapproach\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E539C3C1-3EFB-4B06-A4F3-119B2B3AA7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0EA2E0-FE92-44E4-BFC9-CFD69010A9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{60534445-88EE-4EEC-A086-9C39FBE93AB7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{60534445-88EE-4EEC-A086-9C39FBE93AB7}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSEGNE" sheetId="1" r:id="rId1"/>
@@ -9788,7 +9788,7 @@
         <v>67.138559999999998</v>
       </c>
       <c r="F3" s="11">
-        <v>1.1000000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="G3" s="2">
         <v>50</v>
@@ -10648,7 +10648,7 @@
         <v>66.662399999999991</v>
       </c>
       <c r="F24" s="11">
-        <v>1.1000000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="G24" s="2">
         <v>50</v>
